--- a/forms/trg/Formulir_TRG_aio-rg.xlsx
+++ b/forms/trg/Formulir_TRG_aio-rg.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -690,122 +690,110 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>ID peneliti (SINTA/Scopus/ORCID) banyak yang kosong.</t>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Contoh pengisian (hanya ilustrasi, jangan disalin)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Contoh pengisian (hanya ilustrasi, jangan disalin)</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Nama</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Dr. Contoh Nama, S.Pi., M.Si.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Nama</t>
+          <t>Keahlian utama 1-3 (pilih)</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Dr. Contoh Nama, S.Pi., M.Si.</t>
+          <t>Perikanan &amp; akuakultur; Ekosistem pesisir &amp; laut</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Keahlian utama 1-3 (pilih)</t>
+          <t>Kata kunci keahlian</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Perikanan &amp; akuakultur; Ekosistem pesisir &amp; laut</t>
+          <t>budidaya udang, kualitas air, bioflok</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Kata kunci keahlian</t>
+          <t>SINTA ID</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>budidaya udang, kualitas air, bioflok</t>
+          <t>6012345</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>SINTA ID</t>
+          <t>ORCID</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>6012345</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>ORCID</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
           <t>0000-0002-1234-5678</t>
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Kemajuan pengisian (otomatis)</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Kemajuan pengisian (otomatis)</t>
-        </is>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Anggota tercantum</t>
+        </is>
+      </c>
+      <c r="B24" s="7">
+        <f>COUNTA(Anggota!B5:B19)</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Anggota tercantum</t>
+          <t>Anggota dengan keahlian terpilih</t>
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B18)</f>
+        <f>COUNTA(Anggota!F5:F19)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Anggota dengan keahlian terpilih</t>
-        </is>
-      </c>
-      <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
           <t>Persentase anggota berkeahlian</t>
         </is>
       </c>
-      <c r="B27" s="8">
-        <f>IF(B25=0,0,B26/B25)</f>
+      <c r="B26" s="8">
+        <f>IF(B24=0,0,B25/B24)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,27 +913,35 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Babatunde Olamide Bamgbose</t>
+          <t>Irfan Sugianto</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Bayero University, Kano</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Dentistry</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6679491</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57194060981</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -958,17 +954,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Fadil Hidayat</t>
+          <t>Babatunde Olamide Bamgbose</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Bayero University, Kano</t>
         </is>
       </c>
       <c r="E6" s="11" t="n"/>
@@ -989,9 +985,21 @@
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Muhammad Fadil Hidayat</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
@@ -1000,7 +1008,11 @@
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="12" t="n"/>
-      <c r="M7" s="12" t="n"/>
+      <c r="M7" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1189,15 +1201,32 @@
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="12" t="n"/>
     </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
